--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e0580d0e3bf4257"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f063e05abd4cec"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f063e05abd4cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79fee24924434e4b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R79fee24924434e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0ab5674ce5c4ffd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0ab5674ce5c4ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9264fd7c08d3472f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9264fd7c08d3472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d9dcbb2667a4dde"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d9dcbb2667a4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b95076734d540f2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b95076734d540f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc81d213177f84354"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc81d213177f84354"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb83b09e1b6c44ee5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb83b09e1b6c44ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1259e5deb90d41bc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1259e5deb90d41bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R770b1c0cebc04e80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R770b1c0cebc04e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24ab2b4b5e354719"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24ab2b4b5e354719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R777bda47f3cb4d6b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R777bda47f3cb4d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2df1da048cf4586"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf2df1da048cf4586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5361d27566f423e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf5361d27566f423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad51bc4ad90c4a48"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rad51bc4ad90c4a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc151db21a5324776"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc151db21a5324776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d9f9ea9786349af"/>
   </x:sheets>
 </x:workbook>
 </file>
